--- a/files/me-ADPER8902339483.xlsx
+++ b/files/me-ADPER8902339483.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -626,40 +626,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
+          <t>Analysis of Application of Design Standards for Future Climate Change Adaptive Agricultural Reservoirs Using Cluster Analysis</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
+          <t>Dong-Hyuk Joo, 라 나, Hayoung Kim, Seung-Hwan Yoo, Sang-Hyun Lee</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>67</v>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59-70</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.3.059</t>
+          <t>10.3390/w17243463</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +669,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
@@ -679,40 +683,40 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>농업용 저수지의 홍수기 운영을 위한 상당강우-저류용량-관리수위 곡선 적용성 분석</t>
+          <t>Development and utilization of agricultural and rural climate information systems to respond to climate crisis</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>신길채, 나라, 주동혁, 박상빈, 유승환</t>
+          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35-49</t>
+          <t>1129-1139</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2025.67.4.035</t>
+          <t>10.15531/ksccr.2025.16.5.1129</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -720,7 +724,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -732,45 +738,45 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램 이행점검을 위한 시스템 설계</t>
+          <t>농업용 저수지의 가능최대홍수량 설계를 위한 하류부 피해 산정 방안 적용성 분석</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 유승환, 배승종, 박호철, 최규훈, 성재훈, 최진용, 손정우, 허승오</t>
+          <t>주동혁, 나라, 김하영, 소의건, 송인홍, 이성학, 신길채, 심규현, 허건, 유승환</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55-67</t>
+          <t>59-70</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2025.31.4.055</t>
+          <t>10.5389/KSAE.2025.67.3.059</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -781,16 +787,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
+          <t>농업용 저수지의 홍수기 운영을 위한 상당강우-저류용량-관리수위 곡선 적용성 분석</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
+          <t>신길채, 나라, 주동혁, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -799,26 +805,26 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59-71</t>
+          <t>35-49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.2.059</t>
+          <t>10.5389/KSAE.2025.67.4.035</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -834,52 +840,54 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
+          <t>농업환경보전프로그램 이행점검을 위한 시스템 설계</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
+          <t>나라, 주동혁, 유승환, 배승종, 박호철, 최규훈, 성재훈, 최진용, 손정우, 허승오</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51-68</t>
+          <t>55-67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.5.051</t>
+          <t>10.7851/ksrp.2025.31.4.055</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -887,44 +895,44 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>농업환경보전프로그램 이행단계별 문제점 및 애로사항에 대한 이해당사자별 인식 비교</t>
+          <t>Development of a future weather database based on Shared Socioeconomic Pathways scenarios for assessing climate change vulnerability of agricultural infrastructure</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>김수진, 배승종, 유승환, 나라, 손정우, 허승오</t>
+          <t>Dong-Hyuk Joo, 나라, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국기후변화학회지</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>201-210</t>
+          <t>953-964</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.4.201</t>
+          <t>10.15531/ksccr.2024.15.5.953</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -932,7 +940,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -940,52 +950,56 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
+          <t>The Application of a Smart Nexus for Agriculture in Korea for Assessing the Holistic Impacts of Climate Change</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
+          <t>라 나, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi, Seung-Oh Hur, Pu Reun Yoon, Kwang Soo Kim</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>65</v>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
+          <t>990</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2023.65.1.015</t>
+          <t>10.3390/su16030990</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -997,45 +1011,45 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
+          <t>K-HAS와 비율보정 계수를 이용한 농업용 저수지의 비상연계 용수공급 가능량 분석</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
+          <t>김하영, 이상현, 나라, 주동혁, 유승환</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37-49</t>
+          <t>59-71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2023.29.1.037</t>
+          <t>10.5389/KSAE.2023.65.2.059</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1046,44 +1060,44 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>YOLO v2를 이용한 고해상도 항공영상에서의 태양광발전소 탐지 방법 연구</t>
+          <t>농업용 수로부의 수위 보정을 위한 필터기법별 적용성 분석</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>김하영, 나라, 주동혁, 최규훈, 오윤경</t>
+          <t>주동혁, 나라, 김하영, 최규훈, 윤형창, 박상빈, 유승환</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87-96</t>
+          <t>51-68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.2.087</t>
+          <t>10.5389/KSAE.2023.65.5.051</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1099,16 +1113,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
+          <t>농업환경보전프로그램 이행단계별 문제점 및 애로사항에 대한 이해당사자별 인식 비교</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
+          <t>김수진, 배승종, 유승환, 나라, 손정우, 허승오</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1117,34 +1131,36 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17-26</t>
+          <t>201-210</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.1.017</t>
+          <t>10.7851/ksrp.2023.29.4.201</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1152,16 +1168,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
+          <t>딥러닝 기법을 이용한 농업용저수지 CCTV 영상 기반의 수위계측 방법 개발</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
+          <t>주동혁, 이상현, 최규훈, 유승환, 나라, 김하영, 오창조, 윤광식</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1170,26 +1186,26 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9-24</t>
+          <t>15-26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2022.64.3.009</t>
+          <t>10.5389/KSAE.2023.65.1.015</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1205,16 +1221,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>고해상도 농경지 데이터를 이용한 비료사용 농경지의 암모니아 배출량의 시공간적 변화 분석</t>
+          <t>물-에너지-식량-탄소 넥서스를 이용한 통합물관리 모델 평가 연구 - 영산강 수계를 중심으로 -</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>박진선, 이세연, 홍세운, 나라, 오윤경</t>
+          <t>나라, 박진현, 주동혁, 김하영, 유승환, 오창조, 이상현, 오부영, 허승오</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1223,34 +1239,36 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33-41</t>
+          <t>37-49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2021.27.4.033</t>
+          <t>10.7851/ksrp.2023.29.1.037</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1258,44 +1276,44 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>수리·수문설계시스템 및 비율보정계수 기법을 활용한 농업용 저수지의 홍수기 운영기준 평가</t>
+          <t>YOLO v2를 이용한 고해상도 항공영상에서의 태양광발전소 탐지 방법 연구</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>정형모, 이상현, 김경환, 곽영철, 최은혁, 윤성은, 나라, 주동혁, 유승환, 윤광식</t>
+          <t>김하영, 나라, 주동혁, 최규훈, 오윤경</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97-104</t>
+          <t>87-96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2021.63.4.097</t>
+          <t>10.7851/ksrp.2022.28.2.087</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1303,7 +1321,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1311,53 +1331,269 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>농업경영체 등록정보와 공간정보를 활용한 농지범용화 사업 대상지 선정 방안 개발 및 적용</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>나라, 주동혁, 김하영, 유승환, 곽영철, 김정훈, 이향미, 조은정</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17-26</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10.7851/ksrp.2022.28.1.017</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>농업용저수지의 실시간 수위 보정을 위한 Hampel Filter의 최적 Window Size 분석</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>주동혁, 나라, 김하영, 최규훈, 권재환, 유승환</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9-24</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2022.64.3.009</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>고해상도 농경지 데이터를 이용한 비료사용 농경지의 암모니아 배출량의 시공간적 변화 분석</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>박진선, 이세연, 홍세운, 나라, 오윤경</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>33-41</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10.7851/ksrp.2021.27.4.033</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>수리·수문설계시스템 및 비율보정계수 기법을 활용한 농업용 저수지의 홍수기 운영기준 평가</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>정형모, 이상현, 김경환, 곽영철, 최은혁, 윤성은, 나라, 주동혁, 유승환, 윤광식</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>97-104</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2021.63.4.097</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>필터링 기법을 이용한 농업용저수지 수위자료의 품질관리 방안</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>김경환, 최규훈, 정형모, 주동혁, 나라, 최은혁, 권재환, 유승환</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>한국농공학회논문집</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>83-93</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>10.5389/KSAE.2021.63.5.083</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>세 학회지</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>공저자</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
